--- a/standalone/병실 배정표_122.xlsx
+++ b/standalone/병실 배정표_122.xlsx
@@ -2440,7 +2440,7 @@
       <c r="E18" s="64"/>
       <c r="F18" s="44"/>
       <c r="G18" s="94"/>
-      <c r="H18" s="88"/>
+      <c r="H18" s="96"/>
       <c r="I18" s="94"/>
       <c r="J18" s="95"/>
       <c r="K18" s="94"/>

--- a/standalone/병실 배정표_122.xlsx
+++ b/standalone/병실 배정표_122.xlsx
@@ -14,10 +14,8 @@
   <sheets>
     <sheet name="20260913~20260919" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'[1]병실 배정표'!$A$1:$S$34</definedName>
-  </definedNames>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -548,7 +546,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="50">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -1173,71 +1171,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1284,8 +1271,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1307,9 +1292,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1338,9 +1320,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="12" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1403,9 +1382,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1448,89 +1424,23 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1540,7 +1450,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1549,8 +1458,149 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1575,13 +1625,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>682624</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>365124</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>682625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1881,1367 +1931,1355 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG81"/>
+  <dimension ref="A1:AG82"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="4" customWidth="1"/>
-    <col min="4" max="5" width="12.25" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="4" customWidth="1"/>
-    <col min="7" max="19" width="12.25" style="4" customWidth="1"/>
-    <col min="20" max="22" width="9" style="3"/>
-    <col min="23" max="23" width="14.75" style="4" customWidth="1"/>
-    <col min="24" max="25" width="11.625" style="4" customWidth="1"/>
-    <col min="26" max="26" width="9" style="3"/>
-    <col min="27" max="27" width="25.25" style="4" customWidth="1"/>
-    <col min="28" max="29" width="11.25" style="4" customWidth="1"/>
-    <col min="30" max="30" width="9" style="3"/>
-    <col min="31" max="31" width="12" style="4" customWidth="1"/>
-    <col min="32" max="16384" width="9" style="3"/>
+    <col min="1" max="2" width="10.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="2" customWidth="1"/>
+    <col min="4" max="5" width="12.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="2" customWidth="1"/>
+    <col min="7" max="19" width="12.25" style="2" customWidth="1"/>
+    <col min="20" max="22" width="9" style="1"/>
+    <col min="23" max="23" width="14.75" style="2" customWidth="1"/>
+    <col min="24" max="25" width="11.625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="9" style="1"/>
+    <col min="27" max="27" width="25.25" style="2" customWidth="1"/>
+    <col min="28" max="29" width="11.25" style="2" customWidth="1"/>
+    <col min="30" max="30" width="9" style="1"/>
+    <col min="31" max="31" width="12" style="2" customWidth="1"/>
+    <col min="32" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="87"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+      <c r="R1" s="87"/>
+      <c r="S1" s="87"/>
     </row>
     <row r="2" spans="1:33" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8" t="s">
+      <c r="B2" s="107"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="140" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="10" t="s">
+      <c r="E2" s="77"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="11" t="s">
+      <c r="H2" s="77"/>
+      <c r="I2" s="141" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="10" t="s">
+      <c r="J2" s="77"/>
+      <c r="K2" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="10" t="s">
+      <c r="L2" s="77"/>
+      <c r="M2" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="10" t="s">
+      <c r="N2" s="77"/>
+      <c r="O2" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="10" t="s">
+      <c r="P2" s="77"/>
+      <c r="Q2" s="134"/>
+      <c r="R2" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="9"/>
+      <c r="S2" s="77"/>
     </row>
     <row r="3" spans="1:33" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="15">
+      <c r="A3" s="108"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="136">
         <v>46278</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="15">
+      <c r="E3" s="137"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="136">
         <v>46279</v>
       </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="15">
+      <c r="H3" s="137"/>
+      <c r="I3" s="136">
         <v>46280</v>
       </c>
-      <c r="J3" s="16"/>
-      <c r="K3" s="15">
+      <c r="J3" s="137"/>
+      <c r="K3" s="136">
         <v>46281</v>
       </c>
-      <c r="L3" s="16"/>
-      <c r="M3" s="15">
+      <c r="L3" s="137"/>
+      <c r="M3" s="136">
         <v>46282</v>
       </c>
-      <c r="N3" s="16"/>
-      <c r="O3" s="15">
+      <c r="N3" s="137"/>
+      <c r="O3" s="136">
         <v>46283</v>
       </c>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="15">
+      <c r="P3" s="137"/>
+      <c r="Q3" s="101"/>
+      <c r="R3" s="136">
         <v>46284</v>
       </c>
-      <c r="S3" s="16"/>
+      <c r="S3" s="137"/>
     </row>
     <row r="4" spans="1:33" ht="274.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="23"/>
+      <c r="A4" s="108"/>
+      <c r="B4" s="110"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="131"/>
+      <c r="N4" s="107"/>
+      <c r="O4" s="132"/>
+      <c r="P4" s="130"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="133"/>
+      <c r="S4" s="130"/>
+      <c r="T4" s="3"/>
     </row>
     <row r="5" spans="1:33" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="28"/>
-      <c r="V5" s="31"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="31"/>
-      <c r="Y5" s="32"/>
-      <c r="Z5" s="31"/>
-      <c r="AA5" s="32"/>
-      <c r="AB5" s="31"/>
-      <c r="AC5" s="32"/>
-      <c r="AD5" s="31"/>
-      <c r="AE5" s="32"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="6"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="10"/>
     </row>
     <row r="6" spans="1:33" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="26"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="28"/>
+      <c r="A6" s="108"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="6"/>
     </row>
     <row r="7" spans="1:33" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="27"/>
-      <c r="S7" s="35"/>
-      <c r="W7" s="36"/>
-      <c r="X7" s="37"/>
-      <c r="Y7" s="37"/>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="39"/>
-      <c r="AB7" s="38"/>
-      <c r="AC7" s="40"/>
-      <c r="AD7" s="38"/>
-      <c r="AE7" s="40"/>
-      <c r="AF7" s="38"/>
-      <c r="AG7" s="38"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="13"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="15"/>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="16"/>
+      <c r="AA7" s="17"/>
+      <c r="AB7" s="16"/>
+      <c r="AC7" s="18"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="18"/>
+      <c r="AF7" s="16"/>
+      <c r="AG7" s="16"/>
     </row>
     <row r="8" spans="1:33" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="27"/>
-      <c r="S8" s="28"/>
-      <c r="W8" s="36"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="37"/>
-      <c r="Z8" s="38"/>
-      <c r="AA8" s="39"/>
-      <c r="AB8" s="38"/>
-      <c r="AC8" s="40"/>
-      <c r="AD8" s="38"/>
-      <c r="AE8" s="40"/>
-      <c r="AF8" s="38"/>
-      <c r="AG8" s="38"/>
-    </row>
-    <row r="9" spans="1:33" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="42"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="47"/>
-      <c r="N9" s="49"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="50"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="38"/>
-      <c r="AA9" s="39"/>
-      <c r="AB9" s="40"/>
-      <c r="AC9" s="40"/>
-      <c r="AD9" s="38"/>
-      <c r="AE9" s="40"/>
-      <c r="AF9" s="38"/>
-      <c r="AG9" s="38"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="6"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="15"/>
+      <c r="Y8" s="15"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="16"/>
+      <c r="AC8" s="18"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="18"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="16"/>
+    </row>
+    <row r="9" spans="1:33" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="108"/>
+      <c r="B9" s="110"/>
+      <c r="C9" s="142"/>
+      <c r="D9" s="143"/>
+      <c r="E9" s="144"/>
+      <c r="F9" s="142"/>
+      <c r="G9" s="143"/>
+      <c r="H9" s="145"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="146"/>
+      <c r="K9" s="143"/>
+      <c r="L9" s="146"/>
+      <c r="M9" s="143"/>
+      <c r="N9" s="146"/>
+      <c r="O9" s="143"/>
+      <c r="P9" s="146"/>
+      <c r="Q9" s="142"/>
+      <c r="R9" s="143"/>
+      <c r="S9" s="146"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="15"/>
+      <c r="Y9" s="15"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="18"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="18"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
     </row>
     <row r="10" spans="1:33" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="111"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="26"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="18"/>
+      <c r="AC10" s="18"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="18"/>
+      <c r="AF10" s="16"/>
+      <c r="AG10" s="16"/>
+    </row>
+    <row r="11" spans="1:33" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="57"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="55"/>
-      <c r="N10" s="56"/>
-      <c r="O10" s="55"/>
-      <c r="P10" s="59"/>
-      <c r="Q10" s="60"/>
-      <c r="R10" s="61"/>
-      <c r="S10" s="53"/>
-      <c r="W10" s="36"/>
-      <c r="X10" s="37"/>
-      <c r="Y10" s="37"/>
-      <c r="Z10" s="38"/>
-      <c r="AA10" s="40"/>
-      <c r="AB10" s="40"/>
-      <c r="AC10" s="40"/>
-      <c r="AD10" s="38"/>
-      <c r="AE10" s="40"/>
-      <c r="AF10" s="38"/>
-      <c r="AG10" s="38"/>
-    </row>
-    <row r="11" spans="1:33" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="62" t="s">
+      <c r="B11" s="87"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="36"/>
+      <c r="S11" s="28"/>
+      <c r="W11" s="14"/>
+      <c r="X11" s="15"/>
+      <c r="Y11" s="15"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="18"/>
+      <c r="AB11" s="18"/>
+      <c r="AC11" s="18"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="18"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="16"/>
+    </row>
+    <row r="12" spans="1:33" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="68"/>
-      <c r="K11" s="66"/>
-      <c r="L11" s="69"/>
-      <c r="M11" s="66"/>
-      <c r="N11" s="67"/>
-      <c r="O11" s="66"/>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="64"/>
-      <c r="S11" s="71"/>
-      <c r="W11" s="72"/>
-      <c r="X11" s="37"/>
-      <c r="Y11" s="37"/>
-      <c r="Z11" s="38"/>
-      <c r="AA11" s="72"/>
-      <c r="AB11" s="37"/>
-      <c r="AC11" s="37"/>
-      <c r="AD11" s="38"/>
-      <c r="AE11" s="39"/>
-      <c r="AF11" s="38"/>
-      <c r="AG11" s="38"/>
-    </row>
-    <row r="12" spans="1:33" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="73"/>
-      <c r="L12" s="75"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="28"/>
-      <c r="O12" s="73"/>
-      <c r="P12" s="74"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="73"/>
-      <c r="S12" s="41"/>
-      <c r="W12" s="36"/>
-      <c r="X12" s="37"/>
-      <c r="Y12" s="37"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="36"/>
-      <c r="AB12" s="37"/>
-      <c r="AC12" s="37"/>
-      <c r="AD12" s="38"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="38"/>
+      <c r="B12" s="107"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="45"/>
+      <c r="W12" s="46"/>
+      <c r="X12" s="15"/>
+      <c r="Y12" s="15"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="46"/>
+      <c r="AB12" s="15"/>
+      <c r="AC12" s="15"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="17"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="16"/>
     </row>
     <row r="13" spans="1:33" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="76"/>
-      <c r="L13" s="75"/>
-      <c r="M13" s="76"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="76"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="26"/>
-      <c r="R13" s="76"/>
-      <c r="S13" s="74"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="32"/>
-      <c r="W13" s="77"/>
-      <c r="X13" s="78"/>
-      <c r="Y13" s="79"/>
-      <c r="Z13" s="78"/>
-      <c r="AA13" s="77"/>
-      <c r="AB13" s="78"/>
-      <c r="AC13" s="79"/>
-      <c r="AD13" s="38"/>
-      <c r="AE13" s="39"/>
-      <c r="AF13" s="38"/>
-      <c r="AG13" s="38"/>
+      <c r="A13" s="108"/>
+      <c r="B13" s="110"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="19"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="15"/>
+      <c r="Y13" s="15"/>
+      <c r="Z13" s="16"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="15"/>
+      <c r="AC13" s="15"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="17"/>
+      <c r="AF13" s="16"/>
+      <c r="AG13" s="16"/>
     </row>
     <row r="14" spans="1:33" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="73"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="73"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="73"/>
-      <c r="P14" s="74"/>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="73"/>
-      <c r="S14" s="74"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="37"/>
-      <c r="Y14" s="37"/>
-      <c r="Z14" s="38"/>
-      <c r="AA14" s="36"/>
-      <c r="AB14" s="37"/>
-      <c r="AC14" s="37"/>
-      <c r="AD14" s="38"/>
-      <c r="AE14" s="40"/>
-      <c r="AF14" s="38"/>
-      <c r="AG14" s="38"/>
-    </row>
-    <row r="15" spans="1:33" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="42"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="81"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="81"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="81"/>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="76"/>
-      <c r="S15" s="50"/>
-      <c r="W15" s="36"/>
-      <c r="X15" s="37"/>
-      <c r="Y15" s="37"/>
-      <c r="Z15" s="38"/>
-      <c r="AA15" s="36"/>
-      <c r="AB15" s="37"/>
-      <c r="AC15" s="37"/>
-      <c r="AD15" s="38"/>
-      <c r="AE15" s="40"/>
-      <c r="AF15" s="38"/>
-      <c r="AG15" s="38"/>
-    </row>
-    <row r="16" spans="1:33" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="83" t="s">
+      <c r="A14" s="108"/>
+      <c r="B14" s="110"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="50"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="50"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="50"/>
+      <c r="S14" s="48"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="51"/>
+      <c r="X14" s="52"/>
+      <c r="Y14" s="53"/>
+      <c r="Z14" s="52"/>
+      <c r="AA14" s="51"/>
+      <c r="AB14" s="52"/>
+      <c r="AC14" s="53"/>
+      <c r="AD14" s="16"/>
+      <c r="AE14" s="17"/>
+      <c r="AF14" s="16"/>
+      <c r="AG14" s="16"/>
+    </row>
+    <row r="15" spans="1:33" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="108"/>
+      <c r="B15" s="110"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="47"/>
+      <c r="S15" s="48"/>
+      <c r="W15" s="14"/>
+      <c r="X15" s="15"/>
+      <c r="Y15" s="15"/>
+      <c r="Z15" s="16"/>
+      <c r="AA15" s="14"/>
+      <c r="AB15" s="15"/>
+      <c r="AC15" s="15"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="18"/>
+      <c r="AF15" s="16"/>
+      <c r="AG15" s="16"/>
+    </row>
+    <row r="16" spans="1:33" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="111"/>
+      <c r="B16" s="88"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="55"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="55"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="50"/>
+      <c r="S16" s="26"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="15"/>
+      <c r="Y16" s="15"/>
+      <c r="Z16" s="16"/>
+      <c r="AA16" s="14"/>
+      <c r="AB16" s="15"/>
+      <c r="AC16" s="15"/>
+      <c r="AD16" s="16"/>
+      <c r="AE16" s="18"/>
+      <c r="AF16" s="16"/>
+      <c r="AG16" s="16"/>
+    </row>
+    <row r="17" spans="1:33" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="125" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="84"/>
-      <c r="H16" s="86"/>
-      <c r="I16" s="84"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="84"/>
-      <c r="L16" s="87"/>
-      <c r="M16" s="84"/>
-      <c r="N16" s="87"/>
-      <c r="O16" s="84"/>
-      <c r="P16" s="87"/>
-      <c r="Q16" s="63"/>
-      <c r="R16" s="84"/>
-      <c r="S16" s="88"/>
-      <c r="T16" s="89"/>
-      <c r="W16" s="40"/>
-      <c r="X16" s="40"/>
-      <c r="Y16" s="40"/>
-      <c r="Z16" s="38"/>
-      <c r="AA16" s="40"/>
-      <c r="AB16" s="40"/>
-      <c r="AC16" s="40"/>
-      <c r="AD16" s="38"/>
-      <c r="AE16" s="40"/>
-      <c r="AF16" s="38"/>
-      <c r="AG16" s="38"/>
-    </row>
-    <row r="17" spans="1:33" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="92"/>
-      <c r="F17" s="90"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="92"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="92"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="64"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="64"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="64"/>
-      <c r="Q17" s="90"/>
-      <c r="R17" s="91"/>
-      <c r="S17" s="93"/>
-      <c r="W17" s="40"/>
-      <c r="X17" s="40"/>
-      <c r="Y17" s="40"/>
-      <c r="Z17" s="38"/>
-      <c r="AA17" s="40"/>
-      <c r="AB17" s="40"/>
-      <c r="AC17" s="40"/>
-      <c r="AD17" s="38"/>
-      <c r="AE17" s="40"/>
-      <c r="AF17" s="38"/>
-      <c r="AG17" s="38"/>
-    </row>
-    <row r="18" spans="1:33" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="95"/>
-      <c r="K18" s="94"/>
-      <c r="L18" s="96"/>
-      <c r="M18" s="94"/>
-      <c r="N18" s="97"/>
-      <c r="O18" s="94"/>
-      <c r="P18" s="96"/>
-      <c r="Q18" s="44"/>
-      <c r="R18" s="94"/>
-      <c r="S18" s="96"/>
-      <c r="W18" s="40"/>
-      <c r="X18" s="40"/>
-      <c r="Y18" s="40"/>
-      <c r="Z18" s="38"/>
-      <c r="AA18" s="40"/>
-      <c r="AB18" s="40"/>
-      <c r="AC18" s="40"/>
-      <c r="AD18" s="38"/>
-      <c r="AE18" s="40"/>
-      <c r="AF18" s="38"/>
-      <c r="AG18" s="38"/>
-    </row>
-    <row r="19" spans="1:33" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="98" t="s">
+      <c r="B17" s="107"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="60"/>
+      <c r="M17" s="57"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="60"/>
+      <c r="Q17" s="37"/>
+      <c r="R17" s="57"/>
+      <c r="S17" s="61"/>
+      <c r="T17" s="62"/>
+      <c r="W17" s="18"/>
+      <c r="X17" s="18"/>
+      <c r="Y17" s="18"/>
+      <c r="Z17" s="16"/>
+      <c r="AA17" s="18"/>
+      <c r="AB17" s="18"/>
+      <c r="AC17" s="18"/>
+      <c r="AD17" s="16"/>
+      <c r="AE17" s="18"/>
+      <c r="AF17" s="16"/>
+      <c r="AG17" s="16"/>
+    </row>
+    <row r="18" spans="1:33" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="108"/>
+      <c r="B18" s="110"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="64"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="63"/>
+      <c r="R18" s="64"/>
+      <c r="S18" s="66"/>
+      <c r="W18" s="18"/>
+      <c r="X18" s="18"/>
+      <c r="Y18" s="18"/>
+      <c r="Z18" s="16"/>
+      <c r="AA18" s="18"/>
+      <c r="AB18" s="18"/>
+      <c r="AC18" s="18"/>
+      <c r="AD18" s="16"/>
+      <c r="AE18" s="18"/>
+      <c r="AF18" s="16"/>
+      <c r="AG18" s="16"/>
+    </row>
+    <row r="19" spans="1:33" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="111"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="67"/>
+      <c r="L19" s="69"/>
+      <c r="M19" s="67"/>
+      <c r="N19" s="70"/>
+      <c r="O19" s="67"/>
+      <c r="P19" s="69"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="69"/>
+      <c r="W19" s="18"/>
+      <c r="X19" s="18"/>
+      <c r="Y19" s="18"/>
+      <c r="Z19" s="16"/>
+      <c r="AA19" s="18"/>
+      <c r="AB19" s="18"/>
+      <c r="AC19" s="18"/>
+      <c r="AD19" s="16"/>
+      <c r="AE19" s="18"/>
+      <c r="AF19" s="16"/>
+      <c r="AG19" s="16"/>
+    </row>
+    <row r="20" spans="1:33" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="126" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="99"/>
-      <c r="C19" s="100" t="s">
+      <c r="B20" s="90"/>
+      <c r="C20" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="101"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="101"/>
-      <c r="G19" s="101"/>
-      <c r="H19" s="101"/>
-      <c r="I19" s="102" t="s">
+      <c r="D20" s="92"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="92"/>
+      <c r="H20" s="92"/>
+      <c r="I20" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="102" t="s">
+      <c r="J20" s="87"/>
+      <c r="K20" s="87"/>
+      <c r="L20" s="87"/>
+      <c r="M20" s="88"/>
+      <c r="N20" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="43"/>
-      <c r="W19" s="40"/>
-      <c r="X19" s="40"/>
-      <c r="Y19" s="40"/>
-      <c r="Z19" s="38"/>
-      <c r="AA19" s="40"/>
-      <c r="AB19" s="40"/>
-      <c r="AC19" s="40"/>
-      <c r="AD19" s="38"/>
-      <c r="AE19" s="40"/>
-      <c r="AF19" s="38"/>
-      <c r="AG19" s="38"/>
-    </row>
-    <row r="20" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="O20" s="87"/>
+      <c r="P20" s="87"/>
+      <c r="Q20" s="87"/>
+      <c r="R20" s="87"/>
+      <c r="S20" s="88"/>
+      <c r="W20" s="18"/>
+      <c r="X20" s="18"/>
+      <c r="Y20" s="18"/>
+      <c r="Z20" s="16"/>
+      <c r="AA20" s="18"/>
+      <c r="AB20" s="18"/>
+      <c r="AC20" s="18"/>
+      <c r="AD20" s="16"/>
+      <c r="AE20" s="18"/>
+      <c r="AF20" s="16"/>
+      <c r="AG20" s="16"/>
+    </row>
+    <row r="21" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="99"/>
-      <c r="C20" s="104" t="s">
+      <c r="B21" s="90"/>
+      <c r="C21" s="114" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="101"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="101"/>
-      <c r="G20" s="101"/>
-      <c r="H20" s="99"/>
-      <c r="I20" s="104" t="s">
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="92"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="J20" s="101"/>
-      <c r="K20" s="101"/>
-      <c r="L20" s="101"/>
-      <c r="M20" s="99"/>
-      <c r="N20" s="105" t="s">
+      <c r="J21" s="92"/>
+      <c r="K21" s="92"/>
+      <c r="L21" s="92"/>
+      <c r="M21" s="90"/>
+      <c r="N21" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="O20" s="101"/>
-      <c r="P20" s="101"/>
-      <c r="Q20" s="101"/>
-      <c r="R20" s="101"/>
-      <c r="S20" s="99"/>
-      <c r="W20" s="40"/>
-      <c r="X20" s="40"/>
-      <c r="Y20" s="40"/>
-      <c r="Z20" s="38"/>
-      <c r="AA20" s="40"/>
-      <c r="AB20" s="40"/>
-      <c r="AC20" s="40"/>
-      <c r="AD20" s="38"/>
-      <c r="AE20" s="40"/>
-      <c r="AF20" s="38"/>
-      <c r="AG20" s="38"/>
-    </row>
-    <row r="21" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="106" t="s">
+      <c r="O21" s="92"/>
+      <c r="P21" s="92"/>
+      <c r="Q21" s="92"/>
+      <c r="R21" s="92"/>
+      <c r="S21" s="90"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="18"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="16"/>
+      <c r="AA21" s="18"/>
+      <c r="AB21" s="18"/>
+      <c r="AC21" s="18"/>
+      <c r="AD21" s="16"/>
+      <c r="AE21" s="18"/>
+      <c r="AF21" s="16"/>
+      <c r="AG21" s="16"/>
+    </row>
+    <row r="22" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="117" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="99"/>
-      <c r="C21" s="104" t="s">
+      <c r="B22" s="90"/>
+      <c r="C22" s="114" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="101"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="101"/>
-      <c r="G21" s="101"/>
-      <c r="H21" s="99"/>
-      <c r="I21" s="104" t="s">
+      <c r="D22" s="92"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="J21" s="101"/>
-      <c r="K21" s="101"/>
-      <c r="L21" s="101"/>
-      <c r="M21" s="99"/>
-      <c r="N21" s="105" t="s">
+      <c r="J22" s="92"/>
+      <c r="K22" s="92"/>
+      <c r="L22" s="92"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="O21" s="101"/>
-      <c r="P21" s="101"/>
-      <c r="Q21" s="101"/>
-      <c r="R21" s="101"/>
-      <c r="S21" s="99"/>
-      <c r="W21" s="40"/>
-      <c r="X21" s="40"/>
-      <c r="Y21" s="40"/>
-      <c r="Z21" s="38"/>
-      <c r="AA21" s="40"/>
-      <c r="AB21" s="40"/>
-      <c r="AC21" s="40"/>
-      <c r="AD21" s="38"/>
-      <c r="AE21" s="40"/>
-      <c r="AF21" s="38"/>
-      <c r="AG21" s="38"/>
-    </row>
-    <row r="22" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="107" t="s">
+      <c r="O22" s="92"/>
+      <c r="P22" s="92"/>
+      <c r="Q22" s="92"/>
+      <c r="R22" s="92"/>
+      <c r="S22" s="90"/>
+      <c r="W22" s="18"/>
+      <c r="X22" s="18"/>
+      <c r="Y22" s="18"/>
+      <c r="Z22" s="16"/>
+      <c r="AA22" s="18"/>
+      <c r="AB22" s="18"/>
+      <c r="AC22" s="18"/>
+      <c r="AD22" s="16"/>
+      <c r="AE22" s="18"/>
+      <c r="AF22" s="16"/>
+      <c r="AG22" s="16"/>
+    </row>
+    <row r="23" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="99"/>
-      <c r="C22" s="104" t="s">
+      <c r="B23" s="90"/>
+      <c r="C23" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="101"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="101"/>
-      <c r="H22" s="99"/>
-      <c r="I22" s="104" t="s">
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="J22" s="101"/>
-      <c r="K22" s="101"/>
-      <c r="L22" s="101"/>
-      <c r="M22" s="99"/>
-      <c r="N22" s="105" t="s">
+      <c r="J23" s="92"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="92"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="O22" s="101"/>
-      <c r="P22" s="101"/>
-      <c r="Q22" s="101"/>
-      <c r="R22" s="101"/>
-      <c r="S22" s="99"/>
-      <c r="W22" s="40"/>
-      <c r="X22" s="40"/>
-      <c r="Y22" s="40"/>
-      <c r="Z22" s="38"/>
-      <c r="AA22" s="40"/>
-      <c r="AB22" s="40"/>
-      <c r="AC22" s="40"/>
-      <c r="AD22" s="38"/>
-      <c r="AE22" s="40"/>
-      <c r="AF22" s="38"/>
-      <c r="AG22" s="38"/>
-    </row>
-    <row r="23" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="108" t="s">
+      <c r="O23" s="92"/>
+      <c r="P23" s="92"/>
+      <c r="Q23" s="92"/>
+      <c r="R23" s="92"/>
+      <c r="S23" s="90"/>
+      <c r="W23" s="18"/>
+      <c r="X23" s="18"/>
+      <c r="Y23" s="18"/>
+      <c r="Z23" s="16"/>
+      <c r="AA23" s="18"/>
+      <c r="AB23" s="18"/>
+      <c r="AC23" s="18"/>
+      <c r="AD23" s="16"/>
+      <c r="AE23" s="18"/>
+      <c r="AF23" s="16"/>
+      <c r="AG23" s="16"/>
+    </row>
+    <row r="24" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="99"/>
-      <c r="C23" s="104" t="s">
+      <c r="B24" s="90"/>
+      <c r="C24" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="101"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="101"/>
-      <c r="G23" s="101"/>
-      <c r="H23" s="99"/>
-      <c r="I23" s="104" t="s">
+      <c r="D24" s="92"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="92"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="J23" s="101"/>
-      <c r="K23" s="101"/>
-      <c r="L23" s="101"/>
-      <c r="M23" s="99"/>
-      <c r="N23" s="105" t="s">
+      <c r="J24" s="92"/>
+      <c r="K24" s="92"/>
+      <c r="L24" s="92"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="O23" s="101"/>
-      <c r="P23" s="101"/>
-      <c r="Q23" s="101"/>
-      <c r="R23" s="101"/>
-      <c r="S23" s="99"/>
-      <c r="W23" s="40"/>
-      <c r="X23" s="40"/>
-      <c r="Y23" s="40"/>
-      <c r="Z23" s="38"/>
-      <c r="AA23" s="40"/>
-      <c r="AB23" s="40"/>
-      <c r="AC23" s="40"/>
-      <c r="AD23" s="38"/>
-      <c r="AE23" s="40"/>
-      <c r="AF23" s="38"/>
-      <c r="AG23" s="38"/>
-    </row>
-    <row r="24" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="109" t="s">
+      <c r="O24" s="92"/>
+      <c r="P24" s="92"/>
+      <c r="Q24" s="92"/>
+      <c r="R24" s="92"/>
+      <c r="S24" s="90"/>
+      <c r="W24" s="18"/>
+      <c r="X24" s="18"/>
+      <c r="Y24" s="18"/>
+      <c r="Z24" s="16"/>
+      <c r="AA24" s="18"/>
+      <c r="AB24" s="18"/>
+      <c r="AC24" s="18"/>
+      <c r="AD24" s="16"/>
+      <c r="AE24" s="18"/>
+      <c r="AF24" s="16"/>
+      <c r="AG24" s="16"/>
+    </row>
+    <row r="25" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="116" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="99"/>
-      <c r="C24" s="104" t="s">
+      <c r="B25" s="90"/>
+      <c r="C25" s="114" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="101"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="101"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="104" t="s">
+      <c r="D25" s="92"/>
+      <c r="E25" s="92"/>
+      <c r="F25" s="92"/>
+      <c r="G25" s="92"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="114" t="s">
         <v>32</v>
       </c>
-      <c r="J24" s="101"/>
-      <c r="K24" s="101"/>
-      <c r="L24" s="101"/>
-      <c r="M24" s="99"/>
-      <c r="N24" s="110"/>
-      <c r="O24" s="101"/>
-      <c r="P24" s="101"/>
-      <c r="Q24" s="101"/>
-      <c r="R24" s="101"/>
-      <c r="S24" s="99"/>
-      <c r="W24" s="40"/>
-      <c r="X24" s="40"/>
-      <c r="Y24" s="40"/>
-      <c r="Z24" s="38"/>
-      <c r="AA24" s="40"/>
-      <c r="AB24" s="40"/>
-      <c r="AC24" s="40"/>
-      <c r="AD24" s="38"/>
-      <c r="AE24" s="40"/>
-      <c r="AF24" s="38"/>
-      <c r="AG24" s="38"/>
-    </row>
-    <row r="25" spans="1:33" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="111" t="s">
+      <c r="J25" s="92"/>
+      <c r="K25" s="92"/>
+      <c r="L25" s="92"/>
+      <c r="M25" s="90"/>
+      <c r="N25" s="105"/>
+      <c r="O25" s="92"/>
+      <c r="P25" s="92"/>
+      <c r="Q25" s="92"/>
+      <c r="R25" s="92"/>
+      <c r="S25" s="90"/>
+      <c r="W25" s="18"/>
+      <c r="X25" s="18"/>
+      <c r="Y25" s="18"/>
+      <c r="Z25" s="16"/>
+      <c r="AA25" s="18"/>
+      <c r="AB25" s="18"/>
+      <c r="AC25" s="18"/>
+      <c r="AD25" s="16"/>
+      <c r="AE25" s="18"/>
+      <c r="AF25" s="16"/>
+      <c r="AG25" s="16"/>
+    </row>
+    <row r="26" spans="1:33" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="101"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="101"/>
-      <c r="H25" s="101"/>
-      <c r="I25" s="101"/>
-      <c r="J25" s="101"/>
-      <c r="K25" s="101"/>
-      <c r="L25" s="101"/>
-      <c r="M25" s="101"/>
-      <c r="N25" s="101"/>
-      <c r="O25" s="101"/>
-      <c r="P25" s="101"/>
-      <c r="Q25" s="101"/>
-      <c r="R25" s="101"/>
-      <c r="S25" s="99"/>
-      <c r="W25" s="40"/>
-      <c r="X25" s="40"/>
-      <c r="Y25" s="40"/>
-      <c r="Z25" s="38"/>
-      <c r="AA25" s="40"/>
-      <c r="AB25" s="40"/>
-      <c r="AC25" s="40"/>
-      <c r="AD25" s="38"/>
-      <c r="AE25" s="40"/>
-      <c r="AF25" s="38"/>
-      <c r="AG25" s="38"/>
-    </row>
-    <row r="26" spans="1:33" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="112" t="s">
+      <c r="B26" s="92"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="92"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="92"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="92"/>
+      <c r="L26" s="92"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="92"/>
+      <c r="O26" s="92"/>
+      <c r="P26" s="92"/>
+      <c r="Q26" s="92"/>
+      <c r="R26" s="92"/>
+      <c r="S26" s="90"/>
+      <c r="W26" s="18"/>
+      <c r="X26" s="18"/>
+      <c r="Y26" s="18"/>
+      <c r="Z26" s="16"/>
+      <c r="AA26" s="18"/>
+      <c r="AB26" s="18"/>
+      <c r="AC26" s="18"/>
+      <c r="AD26" s="16"/>
+      <c r="AE26" s="18"/>
+      <c r="AF26" s="16"/>
+      <c r="AG26" s="16"/>
+    </row>
+    <row r="27" spans="1:33" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="101"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="101"/>
-      <c r="H26" s="101"/>
-      <c r="I26" s="101"/>
-      <c r="J26" s="101"/>
-      <c r="K26" s="101"/>
-      <c r="L26" s="101"/>
-      <c r="M26" s="101"/>
-      <c r="N26" s="101"/>
-      <c r="O26" s="101"/>
-      <c r="P26" s="101"/>
-      <c r="Q26" s="101"/>
-      <c r="R26" s="101"/>
-      <c r="S26" s="99"/>
-      <c r="W26" s="40"/>
-      <c r="X26" s="40"/>
-      <c r="Y26" s="40"/>
-      <c r="Z26" s="38"/>
-      <c r="AA26" s="40"/>
-      <c r="AB26" s="40"/>
-      <c r="AC26" s="40"/>
-      <c r="AD26" s="38"/>
-      <c r="AE26" s="40"/>
-      <c r="AF26" s="38"/>
-      <c r="AG26" s="38"/>
-    </row>
-    <row r="27" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="113" t="s">
+      <c r="B27" s="92"/>
+      <c r="C27" s="92"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="92"/>
+      <c r="G27" s="92"/>
+      <c r="H27" s="92"/>
+      <c r="I27" s="92"/>
+      <c r="J27" s="92"/>
+      <c r="K27" s="92"/>
+      <c r="L27" s="92"/>
+      <c r="M27" s="92"/>
+      <c r="N27" s="92"/>
+      <c r="O27" s="92"/>
+      <c r="P27" s="92"/>
+      <c r="Q27" s="92"/>
+      <c r="R27" s="92"/>
+      <c r="S27" s="90"/>
+      <c r="W27" s="18"/>
+      <c r="X27" s="18"/>
+      <c r="Y27" s="18"/>
+      <c r="Z27" s="16"/>
+      <c r="AA27" s="18"/>
+      <c r="AB27" s="18"/>
+      <c r="AC27" s="18"/>
+      <c r="AD27" s="16"/>
+      <c r="AE27" s="18"/>
+      <c r="AF27" s="16"/>
+      <c r="AG27" s="16"/>
+    </row>
+    <row r="28" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="114" t="s">
+      <c r="B28" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="115" t="s">
+      <c r="C28" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="116" t="s">
+      <c r="D28" s="88"/>
+      <c r="E28" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="117"/>
-      <c r="L27" s="117"/>
-      <c r="M27" s="117"/>
-      <c r="N27" s="117"/>
-      <c r="O27" s="117"/>
-      <c r="P27" s="117"/>
-      <c r="Q27" s="117"/>
-      <c r="R27" s="117"/>
-      <c r="S27" s="6"/>
-      <c r="W27" s="40"/>
-      <c r="X27" s="40"/>
-      <c r="Y27" s="40"/>
-      <c r="Z27" s="38"/>
-      <c r="AA27" s="40"/>
-      <c r="AB27" s="40"/>
-      <c r="AC27" s="40"/>
-      <c r="AD27" s="38"/>
-      <c r="AE27" s="40"/>
-      <c r="AF27" s="38"/>
-      <c r="AG27" s="38"/>
-    </row>
-    <row r="28" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="14"/>
-      <c r="B28" s="118" t="s">
+      <c r="F28" s="87"/>
+      <c r="G28" s="87"/>
+      <c r="H28" s="87"/>
+      <c r="I28" s="88"/>
+      <c r="J28" s="105"/>
+      <c r="K28" s="106"/>
+      <c r="L28" s="106"/>
+      <c r="M28" s="106"/>
+      <c r="N28" s="106"/>
+      <c r="O28" s="106"/>
+      <c r="P28" s="106"/>
+      <c r="Q28" s="106"/>
+      <c r="R28" s="106"/>
+      <c r="S28" s="107"/>
+      <c r="W28" s="18"/>
+      <c r="X28" s="18"/>
+      <c r="Y28" s="18"/>
+      <c r="Z28" s="16"/>
+      <c r="AA28" s="18"/>
+      <c r="AB28" s="18"/>
+      <c r="AC28" s="18"/>
+      <c r="AD28" s="16"/>
+      <c r="AE28" s="18"/>
+      <c r="AF28" s="16"/>
+      <c r="AG28" s="16"/>
+    </row>
+    <row r="29" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="101"/>
+      <c r="B29" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="119" t="s">
+      <c r="C29" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="99"/>
-      <c r="E28" s="120" t="s">
+      <c r="D29" s="90"/>
+      <c r="E29" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="F28" s="101"/>
-      <c r="G28" s="101"/>
-      <c r="H28" s="101"/>
-      <c r="I28" s="99"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="121"/>
-      <c r="L28" s="121"/>
-      <c r="M28" s="121"/>
-      <c r="N28" s="121"/>
-      <c r="O28" s="121"/>
-      <c r="P28" s="121"/>
-      <c r="Q28" s="121"/>
-      <c r="R28" s="121"/>
-      <c r="S28" s="13"/>
-      <c r="W28" s="40"/>
-      <c r="X28" s="40"/>
-      <c r="Y28" s="36"/>
-      <c r="Z28" s="37"/>
-      <c r="AA28" s="37"/>
-      <c r="AB28" s="40"/>
-      <c r="AC28" s="39"/>
-      <c r="AD28" s="38"/>
-      <c r="AE28" s="40"/>
-      <c r="AF28" s="38"/>
-      <c r="AG28" s="38"/>
-    </row>
-    <row r="29" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="14"/>
-      <c r="B29" s="122" t="s">
+      <c r="F29" s="92"/>
+      <c r="G29" s="92"/>
+      <c r="H29" s="92"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="108"/>
+      <c r="K29" s="109"/>
+      <c r="L29" s="109"/>
+      <c r="M29" s="109"/>
+      <c r="N29" s="109"/>
+      <c r="O29" s="109"/>
+      <c r="P29" s="109"/>
+      <c r="Q29" s="109"/>
+      <c r="R29" s="109"/>
+      <c r="S29" s="110"/>
+      <c r="W29" s="18"/>
+      <c r="X29" s="18"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="15"/>
+      <c r="AA29" s="15"/>
+      <c r="AB29" s="18"/>
+      <c r="AC29" s="17"/>
+      <c r="AD29" s="16"/>
+      <c r="AE29" s="18"/>
+      <c r="AF29" s="16"/>
+      <c r="AG29" s="16"/>
+    </row>
+    <row r="30" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="101"/>
+      <c r="B30" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="123" t="s">
+      <c r="C30" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="99"/>
-      <c r="E29" s="120" t="s">
+      <c r="D30" s="90"/>
+      <c r="E30" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="101"/>
-      <c r="G29" s="101"/>
-      <c r="H29" s="101"/>
-      <c r="I29" s="99"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="121"/>
-      <c r="L29" s="121"/>
-      <c r="M29" s="121"/>
-      <c r="N29" s="121"/>
-      <c r="O29" s="121"/>
-      <c r="P29" s="121"/>
-      <c r="Q29" s="121"/>
-      <c r="R29" s="121"/>
-      <c r="S29" s="13"/>
-      <c r="W29" s="40"/>
-      <c r="X29" s="40"/>
-      <c r="Y29" s="36"/>
-      <c r="Z29" s="37"/>
-      <c r="AA29" s="37"/>
-      <c r="AB29" s="40"/>
-      <c r="AC29" s="39"/>
-      <c r="AD29" s="38"/>
-      <c r="AE29" s="40"/>
-      <c r="AF29" s="38"/>
-      <c r="AG29" s="38"/>
-    </row>
-    <row r="30" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="14"/>
-      <c r="B30" s="122" t="s">
+      <c r="F30" s="92"/>
+      <c r="G30" s="92"/>
+      <c r="H30" s="92"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="108"/>
+      <c r="K30" s="109"/>
+      <c r="L30" s="109"/>
+      <c r="M30" s="109"/>
+      <c r="N30" s="109"/>
+      <c r="O30" s="109"/>
+      <c r="P30" s="109"/>
+      <c r="Q30" s="109"/>
+      <c r="R30" s="109"/>
+      <c r="S30" s="110"/>
+      <c r="W30" s="18"/>
+      <c r="X30" s="18"/>
+      <c r="Y30" s="14"/>
+      <c r="Z30" s="15"/>
+      <c r="AA30" s="15"/>
+      <c r="AB30" s="18"/>
+      <c r="AC30" s="17"/>
+      <c r="AD30" s="16"/>
+      <c r="AE30" s="18"/>
+      <c r="AF30" s="16"/>
+      <c r="AG30" s="16"/>
+    </row>
+    <row r="31" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="101"/>
+      <c r="B31" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="123" t="s">
+      <c r="C31" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="99"/>
-      <c r="E30" s="120" t="s">
+      <c r="D31" s="90"/>
+      <c r="E31" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="101"/>
-      <c r="G30" s="101"/>
-      <c r="H30" s="101"/>
-      <c r="I30" s="99"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="121"/>
-      <c r="L30" s="121"/>
-      <c r="M30" s="121"/>
-      <c r="N30" s="121"/>
-      <c r="O30" s="121"/>
-      <c r="P30" s="121"/>
-      <c r="Q30" s="121"/>
-      <c r="R30" s="121"/>
-      <c r="S30" s="13"/>
-      <c r="W30" s="40"/>
-      <c r="X30" s="40"/>
-      <c r="Y30" s="36"/>
-      <c r="Z30" s="37"/>
-      <c r="AA30" s="37"/>
-      <c r="AB30" s="40"/>
-      <c r="AC30" s="39"/>
-      <c r="AD30" s="38"/>
-      <c r="AE30" s="40"/>
-      <c r="AF30" s="38"/>
-      <c r="AG30" s="38"/>
-    </row>
-    <row r="31" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="124"/>
-      <c r="B31" s="122" t="s">
+      <c r="F31" s="92"/>
+      <c r="G31" s="92"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="90"/>
+      <c r="J31" s="108"/>
+      <c r="K31" s="109"/>
+      <c r="L31" s="109"/>
+      <c r="M31" s="109"/>
+      <c r="N31" s="109"/>
+      <c r="O31" s="109"/>
+      <c r="P31" s="109"/>
+      <c r="Q31" s="109"/>
+      <c r="R31" s="109"/>
+      <c r="S31" s="110"/>
+      <c r="W31" s="18"/>
+      <c r="X31" s="18"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="15"/>
+      <c r="AA31" s="15"/>
+      <c r="AB31" s="18"/>
+      <c r="AC31" s="17"/>
+      <c r="AD31" s="16"/>
+      <c r="AE31" s="18"/>
+      <c r="AF31" s="16"/>
+      <c r="AG31" s="16"/>
+    </row>
+    <row r="32" spans="1:33" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="102"/>
+      <c r="B32" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="123" t="s">
+      <c r="C32" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="99"/>
-      <c r="E31" s="120" t="s">
+      <c r="D32" s="90"/>
+      <c r="E32" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="101"/>
-      <c r="G31" s="101"/>
-      <c r="H31" s="101"/>
-      <c r="I31" s="99"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="43"/>
-      <c r="W31" s="40"/>
-      <c r="X31" s="40"/>
-      <c r="Y31" s="36"/>
-      <c r="Z31" s="37"/>
-      <c r="AA31" s="37"/>
-      <c r="AB31" s="40"/>
-      <c r="AC31" s="39"/>
-      <c r="AD31" s="38"/>
-      <c r="AE31" s="38"/>
-      <c r="AF31" s="38"/>
-      <c r="AG31" s="38"/>
-    </row>
-    <row r="32" spans="1:33" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="125" t="s">
+      <c r="F32" s="92"/>
+      <c r="G32" s="92"/>
+      <c r="H32" s="92"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="87"/>
+      <c r="L32" s="87"/>
+      <c r="M32" s="87"/>
+      <c r="N32" s="87"/>
+      <c r="O32" s="87"/>
+      <c r="P32" s="87"/>
+      <c r="Q32" s="87"/>
+      <c r="R32" s="87"/>
+      <c r="S32" s="88"/>
+      <c r="W32" s="18"/>
+      <c r="X32" s="18"/>
+      <c r="Y32" s="14"/>
+      <c r="Z32" s="15"/>
+      <c r="AA32" s="15"/>
+      <c r="AB32" s="18"/>
+      <c r="AC32" s="17"/>
+      <c r="AD32" s="16"/>
+      <c r="AE32" s="16"/>
+      <c r="AF32" s="16"/>
+      <c r="AG32" s="16"/>
+    </row>
+    <row r="33" spans="1:33" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="126" t="s">
+      <c r="B33" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="127"/>
-      <c r="D32" s="127"/>
-      <c r="E32" s="127"/>
-      <c r="F32" s="127"/>
-      <c r="G32" s="127"/>
-      <c r="H32" s="127"/>
-      <c r="I32" s="128"/>
-      <c r="J32" s="129" t="s">
+      <c r="C33" s="76"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="97"/>
+      <c r="J33" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="K32" s="127"/>
-      <c r="L32" s="127"/>
-      <c r="M32" s="127"/>
-      <c r="N32" s="127"/>
-      <c r="O32" s="127"/>
-      <c r="P32" s="127"/>
-      <c r="Q32" s="127"/>
-      <c r="R32" s="127"/>
-      <c r="S32" s="9"/>
-      <c r="W32" s="40"/>
-      <c r="X32" s="40"/>
-      <c r="Y32" s="36"/>
-      <c r="Z32" s="37"/>
-      <c r="AA32" s="37"/>
-      <c r="AB32" s="40"/>
-      <c r="AC32" s="40"/>
-      <c r="AD32" s="38"/>
-      <c r="AE32" s="40"/>
-      <c r="AF32" s="38"/>
-      <c r="AG32" s="38"/>
-    </row>
-    <row r="33" spans="1:33" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="130"/>
-      <c r="B33" s="131" t="s">
+      <c r="K33" s="76"/>
+      <c r="L33" s="76"/>
+      <c r="M33" s="76"/>
+      <c r="N33" s="76"/>
+      <c r="O33" s="76"/>
+      <c r="P33" s="76"/>
+      <c r="Q33" s="76"/>
+      <c r="R33" s="76"/>
+      <c r="S33" s="77"/>
+      <c r="W33" s="18"/>
+      <c r="X33" s="18"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="15"/>
+      <c r="AA33" s="15"/>
+      <c r="AB33" s="18"/>
+      <c r="AC33" s="18"/>
+      <c r="AD33" s="16"/>
+      <c r="AE33" s="18"/>
+      <c r="AF33" s="16"/>
+      <c r="AG33" s="16"/>
+    </row>
+    <row r="34" spans="1:33" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="94"/>
+      <c r="B34" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="132"/>
-      <c r="D33" s="132"/>
-      <c r="E33" s="132"/>
-      <c r="F33" s="132"/>
-      <c r="G33" s="132"/>
-      <c r="H33" s="132"/>
-      <c r="I33" s="133"/>
-      <c r="J33" s="134" t="s">
+      <c r="C34" s="79"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="79"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="80"/>
+      <c r="J34" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="K33" s="132"/>
-      <c r="L33" s="132"/>
-      <c r="M33" s="132"/>
-      <c r="N33" s="132"/>
-      <c r="O33" s="132"/>
-      <c r="P33" s="132"/>
-      <c r="Q33" s="132"/>
-      <c r="R33" s="132"/>
-      <c r="S33" s="135"/>
-      <c r="W33" s="40"/>
-      <c r="X33" s="40"/>
-      <c r="Y33" s="72"/>
-      <c r="Z33" s="37"/>
-      <c r="AA33" s="37"/>
-      <c r="AB33" s="40"/>
-      <c r="AC33" s="72"/>
-      <c r="AD33" s="37"/>
-      <c r="AE33" s="37"/>
-      <c r="AF33" s="38"/>
-      <c r="AG33" s="39"/>
-    </row>
-    <row r="34" spans="1:33" ht="68.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="136"/>
-      <c r="B34" s="137" t="s">
+      <c r="K34" s="79"/>
+      <c r="L34" s="79"/>
+      <c r="M34" s="79"/>
+      <c r="N34" s="79"/>
+      <c r="O34" s="79"/>
+      <c r="P34" s="79"/>
+      <c r="Q34" s="79"/>
+      <c r="R34" s="79"/>
+      <c r="S34" s="82"/>
+      <c r="W34" s="18"/>
+      <c r="X34" s="18"/>
+      <c r="Y34" s="46"/>
+      <c r="Z34" s="15"/>
+      <c r="AA34" s="15"/>
+      <c r="AB34" s="18"/>
+      <c r="AC34" s="46"/>
+      <c r="AD34" s="15"/>
+      <c r="AE34" s="15"/>
+      <c r="AF34" s="16"/>
+      <c r="AG34" s="17"/>
+    </row>
+    <row r="35" spans="1:33" ht="68.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="95"/>
+      <c r="B35" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="138"/>
-      <c r="D34" s="138"/>
-      <c r="E34" s="138"/>
-      <c r="F34" s="138"/>
-      <c r="G34" s="138"/>
-      <c r="H34" s="138"/>
-      <c r="I34" s="139"/>
-      <c r="J34" s="140" t="s">
+      <c r="C35" s="84"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
+      <c r="I35" s="85"/>
+      <c r="J35" s="86" t="s">
         <v>52</v>
       </c>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="43"/>
-      <c r="W34" s="40"/>
-      <c r="X34" s="40"/>
-      <c r="Y34" s="36"/>
-      <c r="Z34" s="37"/>
-      <c r="AA34" s="37"/>
-      <c r="AB34" s="40"/>
-      <c r="AC34" s="36"/>
-      <c r="AD34" s="37"/>
-      <c r="AE34" s="37"/>
-      <c r="AF34" s="38"/>
-      <c r="AG34" s="39"/>
-    </row>
-    <row r="35" spans="1:33" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W35" s="40"/>
-      <c r="X35" s="78"/>
-      <c r="Y35" s="77"/>
-      <c r="Z35" s="78"/>
-      <c r="AA35" s="79"/>
-      <c r="AB35" s="78"/>
-      <c r="AC35" s="77"/>
-      <c r="AD35" s="78"/>
-      <c r="AE35" s="79"/>
-      <c r="AF35" s="38"/>
-      <c r="AG35" s="39"/>
-    </row>
-    <row r="36" spans="1:33" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W36" s="40"/>
-      <c r="X36" s="40"/>
-      <c r="Y36" s="36"/>
-      <c r="Z36" s="37"/>
-      <c r="AA36" s="37"/>
-      <c r="AB36" s="40"/>
-      <c r="AC36" s="36"/>
-      <c r="AD36" s="37"/>
-      <c r="AE36" s="37"/>
-      <c r="AF36" s="38"/>
-      <c r="AG36" s="38"/>
-    </row>
-    <row r="37" spans="1:33" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W37" s="40"/>
-      <c r="X37" s="40"/>
-      <c r="Y37" s="36"/>
-      <c r="Z37" s="37"/>
-      <c r="AA37" s="37"/>
-      <c r="AB37" s="40"/>
-      <c r="AC37" s="36"/>
-      <c r="AD37" s="37"/>
-      <c r="AE37" s="37"/>
-      <c r="AF37" s="38"/>
-      <c r="AG37" s="38"/>
-    </row>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E57" s="141"/>
+      <c r="K35" s="87"/>
+      <c r="L35" s="87"/>
+      <c r="M35" s="87"/>
+      <c r="N35" s="87"/>
+      <c r="O35" s="87"/>
+      <c r="P35" s="87"/>
+      <c r="Q35" s="87"/>
+      <c r="R35" s="87"/>
+      <c r="S35" s="88"/>
+      <c r="W35" s="18"/>
+      <c r="X35" s="18"/>
+      <c r="Y35" s="14"/>
+      <c r="Z35" s="15"/>
+      <c r="AA35" s="15"/>
+      <c r="AB35" s="18"/>
+      <c r="AC35" s="14"/>
+      <c r="AD35" s="15"/>
+      <c r="AE35" s="15"/>
+      <c r="AF35" s="16"/>
+      <c r="AG35" s="17"/>
+    </row>
+    <row r="36" spans="1:33" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W36" s="18"/>
+      <c r="X36" s="52"/>
+      <c r="Y36" s="51"/>
+      <c r="Z36" s="52"/>
+      <c r="AA36" s="53"/>
+      <c r="AB36" s="52"/>
+      <c r="AC36" s="51"/>
+      <c r="AD36" s="52"/>
+      <c r="AE36" s="53"/>
+      <c r="AF36" s="16"/>
+      <c r="AG36" s="17"/>
+    </row>
+    <row r="37" spans="1:33" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W37" s="18"/>
+      <c r="X37" s="18"/>
+      <c r="Y37" s="14"/>
+      <c r="Z37" s="15"/>
+      <c r="AA37" s="15"/>
+      <c r="AB37" s="18"/>
+      <c r="AC37" s="14"/>
+      <c r="AD37" s="15"/>
+      <c r="AE37" s="15"/>
+      <c r="AF37" s="16"/>
+      <c r="AG37" s="16"/>
+    </row>
+    <row r="38" spans="1:33" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W38" s="18"/>
+      <c r="X38" s="18"/>
+      <c r="Y38" s="14"/>
+      <c r="Z38" s="15"/>
+      <c r="AA38" s="15"/>
+      <c r="AB38" s="18"/>
+      <c r="AC38" s="14"/>
+      <c r="AD38" s="15"/>
+      <c r="AE38" s="15"/>
+      <c r="AF38" s="16"/>
+      <c r="AG38" s="16"/>
     </row>
     <row r="58" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E58" s="141"/>
+      <c r="E58" s="74"/>
     </row>
     <row r="59" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E59" s="141"/>
+      <c r="E59" s="74"/>
     </row>
     <row r="60" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E60" s="141"/>
+      <c r="E60" s="74"/>
     </row>
     <row r="61" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E61" s="141"/>
+      <c r="E61" s="74"/>
     </row>
     <row r="62" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E62" s="141"/>
+      <c r="E62" s="74"/>
     </row>
     <row r="63" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E63" s="141"/>
+      <c r="E63" s="74"/>
     </row>
     <row r="64" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E64" s="141"/>
+      <c r="E64" s="74"/>
     </row>
     <row r="65" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E65" s="141"/>
+      <c r="E65" s="74"/>
     </row>
     <row r="66" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E66" s="141"/>
+      <c r="E66" s="74"/>
     </row>
     <row r="67" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E67" s="141"/>
+      <c r="E67" s="74"/>
     </row>
     <row r="68" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E68" s="141"/>
+      <c r="E68" s="74"/>
     </row>
     <row r="69" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E69" s="141"/>
+      <c r="E69" s="74"/>
     </row>
     <row r="70" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E70" s="141"/>
+      <c r="E70" s="74"/>
     </row>
     <row r="71" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E71" s="141"/>
+      <c r="E71" s="74"/>
     </row>
     <row r="72" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E72" s="141"/>
+      <c r="E72" s="74"/>
     </row>
     <row r="73" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E73" s="141"/>
+      <c r="E73" s="74"/>
     </row>
     <row r="74" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E74" s="141"/>
+      <c r="E74" s="74"/>
     </row>
     <row r="75" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E75" s="141"/>
+      <c r="E75" s="74"/>
     </row>
     <row r="76" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E76" s="141"/>
+      <c r="E76" s="74"/>
     </row>
     <row r="77" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E77" s="141"/>
+      <c r="E77" s="74"/>
     </row>
     <row r="78" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E78" s="141"/>
+      <c r="E78" s="74"/>
     </row>
     <row r="79" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E79" s="141"/>
+      <c r="E79" s="74"/>
     </row>
     <row r="80" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E80" s="141"/>
+      <c r="E80" s="74"/>
     </row>
     <row r="81" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E81" s="141"/>
+      <c r="E81" s="74"/>
+    </row>
+    <row r="82" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E82" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="75">
-    <mergeCell ref="J32:S32"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="J33:S33"/>
-    <mergeCell ref="B34:I34"/>
-    <mergeCell ref="J34:S34"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:I30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:I31"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="A25:S25"/>
-    <mergeCell ref="A26:S26"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:I27"/>
-    <mergeCell ref="J27:S31"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:I28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:I29"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:H23"/>
-    <mergeCell ref="I23:M23"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="I24:M24"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="I21:M21"/>
-    <mergeCell ref="N21:S21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="I22:M22"/>
-    <mergeCell ref="N22:S22"/>
-    <mergeCell ref="I19:M19"/>
-    <mergeCell ref="N19:S19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="I20:M20"/>
-    <mergeCell ref="N20:S20"/>
-    <mergeCell ref="A5:B9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:B15"/>
-    <mergeCell ref="A16:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="Q2:Q4"/>
     <mergeCell ref="R2:S2"/>
@@ -3253,16 +3291,60 @@
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="A5:B10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:B16"/>
+    <mergeCell ref="A17:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="I20:M20"/>
+    <mergeCell ref="N20:S20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="I21:M21"/>
+    <mergeCell ref="N21:S21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="N22:S22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="I23:M23"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="I24:M24"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="I25:M25"/>
+    <mergeCell ref="N25:S25"/>
+    <mergeCell ref="A26:S26"/>
+    <mergeCell ref="A27:S27"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:I28"/>
+    <mergeCell ref="J28:S32"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:I30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:I31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:I32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="J33:S33"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="J34:S34"/>
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="J35:S35"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/standalone/병실 배정표_122.xlsx
+++ b/standalone/병실 배정표_122.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rms6654\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12300" windowHeight="5475"/>
   </bookViews>
